--- a/data/cox_xlsx/DFDS.CO.xlsx
+++ b/data/cox_xlsx/DFDS.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="532">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -948,67 +948,70 @@
     <t>Assets</t>
   </si>
   <si>
+    <t>Interest-bearing liabilities (not use)</t>
+  </si>
+  <si>
+    <t>Interest-bearing Liabilities</t>
+  </si>
+  <si>
+    <t>lease liabilities</t>
+  </si>
+  <si>
+    <t>Issued corporate bonds</t>
+  </si>
+  <si>
+    <t>Current Portion of Long-Term Debt excluding Capitalized Leases</t>
+  </si>
+  <si>
+    <t>Interest bearing liabilities- ST - Balancing value</t>
+  </si>
+  <si>
+    <t>Other current liabilities</t>
+  </si>
+  <si>
+    <t>Trade payables</t>
+  </si>
+  <si>
+    <t>Corporation tax</t>
+  </si>
+  <si>
+    <t>Other payables</t>
+  </si>
+  <si>
+    <t>Payables to associates and joint ventures</t>
+  </si>
+  <si>
+    <t>Other Provisions</t>
+  </si>
+  <si>
+    <t>Prepayments from customers</t>
+  </si>
+  <si>
+    <t>Accrued interests</t>
+  </si>
+  <si>
+    <t>Public authorities (VAT, duty, etc)</t>
+  </si>
+  <si>
+    <t>Holiday pay obligations</t>
+  </si>
+  <si>
+    <t>Prepayments from customers - Balancing value</t>
+  </si>
+  <si>
+    <t>Transfers Assets Held for Sale</t>
+  </si>
+  <si>
+    <t>Liabilities Held for Sale</t>
+  </si>
+  <si>
+    <t>Balancing Item - Current Liabilities</t>
+  </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
     <t>Interest-bearing liabilities</t>
-  </si>
-  <si>
-    <t>Interest-bearing Liabilities</t>
-  </si>
-  <si>
-    <t>lease liabilities</t>
-  </si>
-  <si>
-    <t>Issued corporate bonds</t>
-  </si>
-  <si>
-    <t>Current Portion of Long-Term Debt excluding Capitalized Leases</t>
-  </si>
-  <si>
-    <t>Interest bearing liabilities- ST - Balancing value</t>
-  </si>
-  <si>
-    <t>Other current liabilities</t>
-  </si>
-  <si>
-    <t>Trade payables</t>
-  </si>
-  <si>
-    <t>Corporation tax</t>
-  </si>
-  <si>
-    <t>Other payables</t>
-  </si>
-  <si>
-    <t>Payables to associates and joint ventures</t>
-  </si>
-  <si>
-    <t>Other Provisions</t>
-  </si>
-  <si>
-    <t>Prepayments from customers</t>
-  </si>
-  <si>
-    <t>Accrued interests</t>
-  </si>
-  <si>
-    <t>Public authorities (VAT, duty, etc)</t>
-  </si>
-  <si>
-    <t>Holiday pay obligations</t>
-  </si>
-  <si>
-    <t>Prepayments from customers - Balancing value</t>
-  </si>
-  <si>
-    <t>Transfers Assets Held for Sale</t>
-  </si>
-  <si>
-    <t>Liabilities Held for Sale</t>
-  </si>
-  <si>
-    <t>Balancing Item - Current Liabilities</t>
-  </si>
-  <si>
-    <t>Current liabilities</t>
   </si>
   <si>
     <t>Mortgage/Land</t>
@@ -17840,7 +17843,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B128" s="15">
         <v>22901.1</v>
@@ -17895,7 +17898,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="B129" s="15">
         <v>13555.26</v>
@@ -17966,7 +17969,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B130" s="16">
         <v>2651.26</v>
@@ -18025,7 +18028,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B131" s="16">
         <v>6694.58</v>
@@ -18090,7 +18093,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B132" s="16">
         <v>4209.42</v>
@@ -18119,7 +18122,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -18168,7 +18171,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -18327,7 +18330,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B137" s="16">
         <v>194.57</v>
@@ -18469,7 +18472,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="22">
@@ -18549,7 +18552,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B141" s="19">
         <v>24122.33</v>
@@ -18620,7 +18623,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -18651,7 +18654,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="17">
@@ -18684,7 +18687,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B144" s="19">
         <v>37443.47</v>
@@ -18755,7 +18758,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B145" s="16">
         <v>1778.05</v>
@@ -18826,7 +18829,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B146" s="15">
         <v>20079.0</v>
@@ -18897,7 +18900,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -18960,7 +18963,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B148" s="21">
         <v>-705.53</v>
@@ -19031,7 +19034,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B149" s="21">
         <v>-760.89</v>
@@ -19080,7 +19083,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B150" s="16">
         <v>123.39</v>
@@ -19129,7 +19132,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -19164,7 +19167,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B152" s="22">
         <v>-69.6</v>
@@ -19213,7 +19216,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B153" s="17">
         <v>1.58</v>
@@ -19256,7 +19259,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -19289,7 +19292,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B155" s="19">
         <v>21151.53</v>
@@ -19360,7 +19363,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B156" s="22">
         <v>-1.58</v>
@@ -19466,7 +19469,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="18" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B158" s="20">
         <v>121.81</v>
@@ -19537,7 +19540,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B159" s="19">
         <v>21271.75</v>
@@ -19608,7 +19611,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="22">
@@ -19639,7 +19642,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="19">
         <v>58715.22</v>
@@ -19710,7 +19713,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B162" s="17">
         <v>52.24</v>
@@ -19781,7 +19784,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B163" s="17">
         <v>56.22</v>
@@ -19852,7 +19855,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B164" s="17">
         <v>3.97</v>
@@ -19923,7 +19926,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B165" s="16">
         <v>3111.59</v>
@@ -19988,7 +19991,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B166" s="15">
         <v>13594.81</v>
@@ -20051,7 +20054,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B167" s="16">
         <v>2187.76</v>
@@ -20114,7 +20117,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B168" s="16">
         <v>1243.37</v>
@@ -20177,7 +20180,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -20216,7 +20219,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B170" s="16">
         <v>1903.02</v>
@@ -20285,7 +20288,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B171" s="16">
         <v>4032.25</v>
@@ -20340,7 +20343,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B172" s="16">
         <v>1675.23</v>
@@ -20381,7 +20384,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B173" s="16">
         <v>2013.75</v>
@@ -20422,7 +20425,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -20477,7 +20480,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -20520,7 +20523,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -20561,7 +20564,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -20602,7 +20605,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B178" s="17">
         <v>52.24</v>
@@ -20673,7 +20676,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B179" s="17">
         <v>1.0</v>
@@ -20744,7 +20747,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B180" s="17">
         <v>3.97</v>
@@ -20815,7 +20818,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B181" s="17">
         <v>56.22</v>
@@ -21724,7 +21727,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22110,70 +22113,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22249,7 +22252,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22347,7 +22350,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B20" s="16">
         <v>5870.22</v>
@@ -22418,7 +22421,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B21" s="21">
         <v>-257.2</v>
@@ -22483,7 +22486,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B22" s="21">
         <v>-156.83</v>
@@ -22514,7 +22517,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B23" s="17">
         <v>7.84</v>
@@ -22545,7 +22548,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B24" s="17">
         <v>31.37</v>
@@ -22576,7 +22579,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B25" s="21">
         <v>-181.92</v>
@@ -22633,7 +22636,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B26" s="17">
         <v>43.91</v>
@@ -22664,7 +22667,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B27" s="22">
         <v>-1.57</v>
@@ -22693,7 +22696,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -22732,7 +22735,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -22765,7 +22768,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -22794,7 +22797,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -22827,7 +22830,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B32" s="16">
         <v>1180.94</v>
@@ -22892,7 +22895,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -22927,7 +22930,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -22962,7 +22965,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -22997,7 +23000,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B36" s="21">
         <v>-114.49</v>
@@ -23062,7 +23065,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B37" s="17">
         <v>98.8</v>
@@ -23093,7 +23096,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B38" s="16">
         <v>1284.45</v>
@@ -23124,7 +23127,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B39" s="21">
         <v>-203.88</v>
@@ -23155,7 +23158,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" s="21">
         <v>-1293.86</v>
@@ -23184,7 +23187,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B41" s="17">
         <v>94.1</v>
@@ -23251,7 +23254,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B42" s="21">
         <v>-1318.96</v>
@@ -23318,7 +23321,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B43" s="21">
         <v>-277.59</v>
@@ -23389,7 +23392,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -23420,7 +23423,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -23451,7 +23454,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -23480,7 +23483,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47" s="22">
         <v>-1.57</v>
@@ -23519,7 +23522,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B48" s="20">
         <v>5175.45</v>
@@ -23590,7 +23593,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B49" s="21">
         <v>-1121.35</v>
@@ -23661,7 +23664,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B50" s="16">
         <v>467.36</v>
@@ -23724,7 +23727,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B51" s="21">
         <v>-1201.33</v>
@@ -23781,7 +23784,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -23834,7 +23837,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B53" s="16">
         <v>1499.31</v>
@@ -23865,7 +23868,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B54" s="21">
         <v>-148.99</v>
@@ -23936,7 +23939,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -23967,7 +23970,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -24030,7 +24033,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B57" s="15">
         <v>0.0</v>
@@ -24061,7 +24064,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B58" s="17">
         <v>3.14</v>
@@ -24092,7 +24095,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B59" s="22">
         <v>-34.5</v>
@@ -24143,7 +24146,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -24178,7 +24181,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -24215,7 +24218,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -24264,7 +24267,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -24295,7 +24298,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -24342,7 +24345,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -24371,7 +24374,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -24412,7 +24415,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -24453,7 +24456,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -24486,7 +24489,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -24523,7 +24526,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="17">
@@ -24562,7 +24565,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B71" s="24">
         <v>-536.36</v>
@@ -24633,7 +24636,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B72" s="16">
         <v>770.04</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B73" s="21">
         <v>-2355.61</v>
@@ -24745,7 +24748,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B74" s="15">
         <v>0.0</v>
@@ -24802,7 +24805,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B75" s="15">
         <v>0.0</v>
@@ -24853,7 +24856,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B76" s="21">
         <v>-2791.61</v>
@@ -24894,7 +24897,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -24953,7 +24956,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B78" s="17">
         <v>64.3</v>
@@ -25002,7 +25005,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B79" s="15">
         <v>0.0</v>
@@ -25069,7 +25072,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -25098,7 +25101,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -25137,7 +25140,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -25184,7 +25187,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -25233,7 +25236,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -25284,7 +25287,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -25339,7 +25342,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -25382,7 +25385,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B87" s="15">
         <v>0.0</v>
@@ -25437,7 +25440,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -25474,7 +25477,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -25503,7 +25506,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -25534,7 +25537,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -25565,7 +25568,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -25598,7 +25601,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -25635,7 +25638,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -25672,7 +25675,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -25709,7 +25712,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -25740,7 +25743,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -25779,7 +25782,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -25808,7 +25811,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B99" s="17">
         <v>14.11</v>
@@ -25845,7 +25848,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B100" s="22">
         <v>-1.57</v>
@@ -25876,7 +25879,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="18" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B101" s="24">
         <v>-4300.33</v>
@@ -25947,7 +25950,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B102" s="16">
         <v>337.19</v>
@@ -26002,7 +26005,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B103" s="22">
         <v>-14.11</v>
@@ -26073,7 +26076,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B104" s="16">
         <v>2513.63</v>
@@ -26144,7 +26147,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B105" s="16">
         <v>2839.5</v>
@@ -26215,7 +26218,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="18" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B106" s="20">
         <v>324.64</v>
@@ -26286,7 +26289,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B107" s="16">
         <v>4637.52</v>
@@ -27235,7 +27238,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -27411,28 +27414,28 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -27912,7 +27915,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -28016,33 +28019,33 @@
         <v>70</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -28077,7 +28080,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B21" s="31">
         <v>32705.72</v>
@@ -28172,7 +28175,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B22" s="31">
         <v>43276.98</v>
@@ -28259,7 +28262,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -28294,7 +28297,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B24" s="32">
         <v>8505.88</v>
@@ -28389,7 +28392,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B25" s="31">
         <v>19516.28</v>
@@ -28476,7 +28479,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -28511,7 +28514,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B27" s="32">
         <v>151.31</v>
@@ -28606,7 +28609,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B28" s="32">
         <v>334.59</v>
@@ -28693,7 +28696,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -28728,7 +28731,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B30" s="34">
         <v>33.37</v>
@@ -28823,7 +28826,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B31" s="34">
         <v>14.83</v>
@@ -28910,7 +28913,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -28945,7 +28948,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B33" s="34">
         <v>0.0</v>
@@ -29040,7 +29043,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B34" s="34">
         <v>1.51</v>
@@ -29127,7 +29130,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B35" s="34">
         <v>0.0</v>
@@ -29222,7 +29225,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B36" s="34">
         <v>1.51</v>
@@ -29309,7 +29312,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -29344,7 +29347,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B38" s="33">
         <v>0.37</v>
@@ -29439,7 +29442,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B39" s="33">
         <v>0.89</v>
@@ -29526,7 +29529,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -29561,7 +29564,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B41" s="33">
         <v>1.41</v>
@@ -29656,7 +29659,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B42" s="33">
         <v>2.27</v>
@@ -29743,7 +29746,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -29778,7 +29781,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B44" s="33">
         <v>0.17</v>
@@ -29873,7 +29876,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B45" s="33">
         <v>0.44</v>
@@ -29960,7 +29963,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -29995,7 +29998,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B47" s="33">
         <v>3.0</v>
@@ -30072,7 +30075,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B48" s="33">
         <v>6.74</v>
@@ -30139,7 +30142,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -30174,7 +30177,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B50" s="33">
         <v>1.77</v>
@@ -30269,7 +30272,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B51" s="33">
         <v>3.26</v>
@@ -30356,7 +30359,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -30391,7 +30394,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B53" s="31"/>
       <c r="C53" s="33">
@@ -30484,7 +30487,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B54" s="33">
         <v>13.17</v>
@@ -30571,7 +30574,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -30606,7 +30609,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B56" s="31"/>
       <c r="C56" s="33">
@@ -30699,7 +30702,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B57" s="33">
         <v>0.89</v>
@@ -30786,7 +30789,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -30821,7 +30824,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B59" s="31"/>
       <c r="C59" s="36">
@@ -30912,7 +30915,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B60" s="31"/>
       <c r="C60" s="36">
@@ -30995,7 +30998,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -31030,7 +31033,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B62" s="33">
         <v>0.67</v>
@@ -31125,7 +31128,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B63" s="33">
         <v>1.03</v>
@@ -31212,7 +31215,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -31247,7 +31250,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B65" s="33">
         <v>5.6</v>
@@ -31340,7 +31343,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B66" s="33">
         <v>6.42</v>
@@ -31427,7 +31430,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B67" s="29"/>
       <c r="C67" s="29"/>
@@ -31462,7 +31465,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B68" s="33">
         <v>6.27</v>
@@ -31557,7 +31560,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="30" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B69" s="33">
         <v>7.56</v>
@@ -31644,7 +31647,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -31679,7 +31682,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="30" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B71" s="33">
         <v>11.99</v>
@@ -31756,7 +31759,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="30" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B72" s="33">
         <v>15.55</v>
